--- a/dataproduct.api/wwwroot/templates/HRC2_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC2_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7608B893-5AB9-413D-A65A-9FED9A9A4391}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E07EC-0B59-4648-B7DD-7BA64EDBF657}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -255,6 +255,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -263,30 +287,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -310,184 +310,45 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>168089</xdr:colOff>
+      <xdr:colOff>145677</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>179293</xdr:rowOff>
+      <xdr:rowOff>100853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>470336</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>974911</xdr:rowOff>
+      <xdr:rowOff>824854</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="Group 3">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{976BAF94-83FC-4DC9-B6CA-321EF35DD714}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{242A47D4-826B-480C-AEFF-EAB25C025212}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr>
-          <a:grpSpLocks noChangeAspect="1"/>
-        </xdr:cNvGrpSpPr>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="168089" y="179293"/>
-          <a:ext cx="2250701" cy="795618"/>
-          <a:chOff x="0" y="1"/>
-          <a:chExt cx="2095500" cy="876300"/>
+          <a:off x="145677" y="100853"/>
+          <a:ext cx="1781424" cy="724001"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="6" name="Picture 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26A0C954-C2D4-46A6-87B3-19A59D284078}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="133350" y="1"/>
-            <a:ext cx="1819275" cy="407343"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:miter lim="800000"/>
-                <a:headEnd/>
-                <a:tailEnd/>
-              </a14:hiddenLine>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="TextBox 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14FDA956-39EE-4520-9E62-1C3DA85F10F1}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1">
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="0" y="382217"/>
-            <a:ext cx="2095500" cy="494084"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="ctr" anchorCtr="0" upright="1">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" algn="ctr">
-              <a:lnSpc>
-                <a:spcPts val="1200"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="800"/>
-              </a:spcAft>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>CÔNG TY CỔ PHẦN THÉP</a:t>
-            </a:r>
-            <a:br>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HÒA PHÁT DUNG QUẤT</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -803,169 +664,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
     </row>
     <row r="2" spans="1:27" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="7" t="s">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="8" t="s">
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA3" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="10" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
+      <c r="M4" s="12"/>
+      <c r="N4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4" t="s">
+      <c r="O4" s="12"/>
+      <c r="P4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4" t="s">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
+      <c r="S4" s="12"/>
+      <c r="T4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4" t="s">
+      <c r="U4" s="12"/>
+      <c r="V4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4" t="s">
+      <c r="W4" s="12"/>
+      <c r="X4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="7"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="11"/>
     </row>
     <row r="5" spans="1:27" ht="36" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="6"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="14"/>
       <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1026,11 +887,16 @@
       <c r="Y5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="7"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
     <mergeCell ref="Z3:Z5"/>
     <mergeCell ref="A2:AA2"/>
     <mergeCell ref="A1:AA1"/>
@@ -1047,11 +913,6 @@
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:Q3"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/dataproduct.api/wwwroot/templates/HRC2_BBXNSL_PhoiTam.xlsx
+++ b/dataproduct.api/wwwroot/templates/HRC2_BBXNSL_PhoiTam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Projects\BIEUMAU_SANXUAT\Source\dataproduct.BE\dataproduct.api\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E07EC-0B59-4648-B7DD-7BA64EDBF657}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E6D718-04F4-438A-8188-A756FCF99893}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11805" xr2:uid="{8D26054B-D371-44B9-99F0-3A3B1380D846}"/>
   </bookViews>
@@ -255,6 +255,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -276,13 +282,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -664,168 +664,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
     </row>
     <row r="2" spans="1:27" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="11" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="4" t="s">
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AA3" s="11" t="s">
+      <c r="AA3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
       <c r="E4" s="14"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="12" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12" t="s">
+      <c r="I4" s="13"/>
+      <c r="J4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12" t="s">
+      <c r="K4" s="13"/>
+      <c r="L4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12" t="s">
+      <c r="M4" s="13"/>
+      <c r="N4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12" t="s">
+      <c r="O4" s="13"/>
+      <c r="P4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12" t="s">
+      <c r="S4" s="13"/>
+      <c r="T4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12" t="s">
+      <c r="U4" s="13"/>
+      <c r="V4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12" t="s">
+      <c r="W4" s="13"/>
+      <c r="X4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="11"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="5"/>
     </row>
     <row r="5" spans="1:27" ht="36" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="14"/>
       <c r="F5" s="1" t="s">
         <v>15</v>
@@ -887,16 +887,11 @@
       <c r="Y5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="11"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F3:Q3"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
     <mergeCell ref="Z3:Z5"/>
     <mergeCell ref="A2:AA2"/>
     <mergeCell ref="A1:AA1"/>
@@ -913,6 +908,11 @@
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
